--- a/www/download/COUNTRY.CAN.zdW13.xlsx
+++ b/www/download/COUNTRY.CAN.zdW13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Canadá</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3720432596379</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.36338223708724</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38427460943857</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.48183278744543</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.48566336709342</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.48453859679937</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.5482992862423</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.56897207355012</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.39701876991229</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29873500614905</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.21096172036363</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13405687946817</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.06932430176669</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.06056911664981</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13781952754438</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13.593</t>
+          <t>0.631665321018867</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.739</t>
+          <t>0.634074140571407</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14.028</t>
+          <t>0.703163023415521</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14.345</t>
+          <t>0.58757299740433</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>0.501515395591299</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>15.048</t>
+          <t>0.387925197597521</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15.199</t>
+          <t>0.296295460012828</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.568</t>
+          <t>0.276601643596048</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>15.902</t>
+          <t>0.208153215205554</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16.166</t>
+          <t>0.170734665699881</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>16.405</t>
+          <t>0.103536744978086</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>16.677</t>
+          <t>0.0631161792455519</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>17.047</t>
+          <t>0.12155334344045</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>17.486</t>
+          <t>0.147471180408575</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>16.875</t>
+          <t>0.276965536536607</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12.163</t>
+          <t>1.20111380380796</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12.209</t>
+          <t>1.32925409927223</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12.429</t>
+          <t>1.51466954788623</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>1.34703642630028</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>13.076</t>
+          <t>1.2523376813654</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13.48</t>
+          <t>1.06519753139934</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13.708</t>
+          <t>0.948543218267695</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.048</t>
+          <t>0.954423794400316</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.355</t>
+          <t>0.823127299154404</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>14.633</t>
+          <t>0.763642168768134</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>14.847</t>
+          <t>0.635161580344293</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>15.135</t>
+          <t>0.58517600248866</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>15.444</t>
+          <t>0.655222141468231</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>15.745</t>
+          <t>0.67091811194675</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>15.433</t>
+          <t>0.818340160987504</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24163.261</t>
+          <t>1.79817557462547</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24606.801</t>
+          <t>1.9798303672622</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24972.061</t>
+          <t>2.13148802996982</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25524.081</t>
+          <t>1.95287341151339</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>26167.659</t>
+          <t>1.86470361220076</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>26709.975</t>
+          <t>1.65985086611753</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26868.102</t>
+          <t>1.50426272508869</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27201.949</t>
+          <t>1.5506651705446</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>27611.262</t>
+          <t>1.42515493410365</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>28349.86</t>
+          <t>1.35899243152717</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>28533.803</t>
+          <t>1.2022210781264</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>28986.532</t>
+          <t>1.1253002804299</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>29625.12</t>
+          <t>1.22329343293044</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>30221.823</t>
+          <t>1.27551675901488</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>28824.294</t>
+          <t>1.44769849673676</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21474.27</t>
+          <t>22926401342.4255</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>21728.47</t>
+          <t>23393047148.8587</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21998.085</t>
+          <t>23193962747.0067</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>22407.136</t>
+          <t>23395733148.2559</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>23096.434</t>
+          <t>24727143171.0065</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23762.495</t>
+          <t>27231804423.0931</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>24065.074</t>
+          <t>27462149030.9869</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24452.873</t>
+          <t>26627767780.2661</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>24822.944</t>
+          <t>27601691539.8955</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25528.033</t>
+          <t>30046441924.0202</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>25761.811</t>
+          <t>30766287478.7462</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>26246.008</t>
+          <t>31533797774.7127</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>26776.738</t>
+          <t>30501539917.3893</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>27188.563</t>
+          <t>31212593901.1659</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>26224.348</t>
+          <t>28475720754.4226</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>10291018287.5601</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>9985126550.68219</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>9472978614.83326</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>10360621654.4345</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>11177327046.029</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>12553972358.9302</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>13548640941.3592</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>13796839491.2018</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>14990942421.3547</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>15948539991.3392</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>17355517276.2366</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>18323399238.3343</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>17891355637.3842</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>17948347455.4281</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>24.88</t>
+          <t>15868390869.642</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>77.76</t>
+          <t>974523.957686296</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>940990.968270188</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>906585.357391117</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>76.01</t>
+          <t>952526.424634674</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>934091.499408965</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>76.32</t>
+          <t>910306.08561155</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>981921.757782813</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>75.35</t>
+          <t>900767.102131251</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>75.36</t>
+          <t>816252.627575255</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>74.96</t>
+          <t>786894.795741854</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>74.58</t>
+          <t>762788.550630965</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>699837.784503609</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>73.28</t>
+          <t>614454.689972241</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>589230.439511011</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>598107.496368013</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>95183.267365107</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>97023.9886869</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>98322.1015839428</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>97763.7399109706</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>103116.873476462</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>106687.505637475</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>102309.331436922</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>105089.28883462</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>113594.149278158</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>128284.732372413</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>138033.590054225</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>145566.015323487</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>166454.795719396</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>182717.355585424</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>166172.58750972</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>197544.616874803</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>203008.214783948</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>200634.774794897</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>200338.593413656</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>220244.082416461</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>15.85</t>
+          <t>246563.984828648</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>241483.514042474</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>239257.689959812</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>265874.06539364</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>318340.418304474</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>349129.903275616</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>373570.991545768</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>19.76</t>
+          <t>407138.522395139</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>456132.825477898</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>387923.554440293</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>78.73</t>
+          <t>1.08670021429773</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>78.97</t>
+          <t>1.1760836103355</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.08</t>
+          <t>1.32219303910011</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>78.85</t>
+          <t>1.16272119051075</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>79.55</t>
+          <t>1.06636469558396</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>79.25</t>
+          <t>0.892826773830411</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>0.776198373185008</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.65</t>
+          <t>0.77235322731003</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>0.655862807100743</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>78.37</t>
+          <t>0.600650154357257</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>77.88</t>
+          <t>0.484358581128745</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>0.43237658348899</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>0.4966299112047</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>77.02</t>
+          <t>0.514822635701061</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>0.652615455110828</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.3720432596379</t>
+          <t>846.083550564009</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.36338223708724</t>
+          <t>817.865057167375</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.38427460943857</t>
+          <t>762.184263926029</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.48183278744543</t>
+          <t>817.069872657924</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.48566336709342</t>
+          <t>854.822935302857</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.48453859679937</t>
+          <t>931.295987936694</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.5482992862423</t>
+          <t>988.383392795716</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.56897207355012</t>
+          <t>982.146081586796</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.39701876991229</t>
+          <t>1044.30511036392</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.29873500614905</t>
+          <t>1089.89594419271</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.21096172036363</t>
+          <t>1168.95982363483</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.13405687946817</t>
+          <t>1210.64517595226</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.06932430176669</t>
+          <t>1158.4686863965</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.06056911664981</t>
+          <t>1139.94094985644</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.13781952754438</t>
+          <t>1028.22600527143</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>12400965888.7956</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>12820222152.5342</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>10954893694.2107</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>12179891313.4716</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>15020063985.9982</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>19443212020.9379</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>20564978914.6285</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>19483752434.7518</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>21505845561.3694</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>24245614388.2349</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>26119555927.1392</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>26366680585.0244</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>25147334846.4832</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>24814414696.6746</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>18185955640.3312</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>13291519452.8017</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>13445899355.3534</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>11431629170.6756</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>12404978315.8315</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>15006935644.038</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>19466942010.8102</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>20661171963.5191</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>19418211098.6694</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>21684177823.7781</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>24214695866.1846</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>26362642975.2217</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>26584675539.189</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>25588047283.1178</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>25511509044.702</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>19068497197.5833</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>-890553564.006102</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.904</t>
+          <t>-625677202.8192</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.991</t>
+          <t>-476735476.464866</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.974</t>
+          <t>-225087002.359927</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>13128341.9601843</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.248</t>
+          <t>-23729989.8723722</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.293</t>
+          <t>-96193048.8905945</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.404</t>
+          <t>65541336.0824891</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.882</t>
+          <t>-178332262.40874</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3.334</t>
+          <t>30918522.0503462</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3.792</t>
+          <t>-243087048.08251</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4.335</t>
+          <t>-217994954.164555</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>4.913</t>
+          <t>-440712436.634529</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>5.281</t>
+          <t>-697094348.027351</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>-882541557.25216</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.026</t>
+          <t>1765.5227262757</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1779.74274636803</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>1769.93899220067</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.099</t>
+          <t>1767.09432772521</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>1766.37593448528</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.332</t>
+          <t>1762.78198032742</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.314</t>
+          <t>1755.56497436683</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.336</t>
+          <t>1740.70977739026</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1729.22599151685</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.798</t>
+          <t>1744.54211130541</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2.047</t>
+          <t>1735.15554520711</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.297</t>
+          <t>1734.09980094793</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.536</t>
+          <t>1733.79888725502</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.698</t>
+          <t>1726.8083542051</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.393</t>
+          <t>1699.26218765843</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>1777.6244246862</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>1790.98941458703</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>1780.2002044156</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>1779.25009498818</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>1777.72139869936</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>1774.9673548936</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1767.7365617697</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>1747.27643539215</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>1736.34168092017</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>1753.67515846465</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1739.29175223236</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1738.14034517797</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.323</t>
+          <t>1737.86476688926</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>1728.37654810334</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.248</t>
+          <t>1708.0610845166</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>63.17</t>
+          <t>212586.247481861</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>63.41</t>
+          <t>227124.703312745</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>240964.027433186</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>244423.644388295</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>276309.688698034</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>319788.323882874</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>305527.004017058</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>293340.303303088</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>324753.164475383</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>374927.434588916</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>416185.066968156</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>447523.281618681</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>479760.62162081</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>511222.713098214</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>377137.545557467</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>120.11</t>
+          <t>6473040604.44297</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>132.93</t>
+          <t>6806403610.80299</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>151.47</t>
+          <t>6919657131.04125</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>7401819602.07182</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>125.23</t>
+          <t>8053958226.94278</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>106.52</t>
+          <t>8985230793.77623</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>94.85</t>
+          <t>8971527073.12969</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>95.44</t>
+          <t>8248503227.79956</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>82.31</t>
+          <t>8081501645.57945</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>76.36</t>
+          <t>9189869439.52487</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>63.52</t>
+          <t>9146409186.24705</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>58.52</t>
+          <t>9319966368.56365</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>8768012793.46858</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>67.09</t>
+          <t>8673145908.84007</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>81.83</t>
+          <t>6606078675.72871</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>179.82</t>
+          <t>183666.011583961</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>197.98</t>
+          <t>191782.196666642</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>213.15</t>
+          <t>215113.236308681</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>195.29</t>
+          <t>218842.694333262</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>186.47</t>
+          <t>238488.834750277</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>165.99</t>
+          <t>263380.937661185</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>150.43</t>
+          <t>251390.990117605</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>155.07</t>
+          <t>248272.018594687</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>142.52</t>
+          <t>277697.277630295</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>135.9</t>
+          <t>315849.234990461</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>120.22</t>
+          <t>355455.46037644</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>112.53</t>
+          <t>394786.217441356</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>122.33</t>
+          <t>429994.463429775</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>127.55</t>
+          <t>465299.236218921</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>144.77</t>
+          <t>381023.52742129</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>24163.261</t>
+          <t>14888241967.2187</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>24606.801</t>
+          <t>14954755221.9508</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>24972.061</t>
+          <t>14746402063.3969</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25524.081</t>
+          <t>16298284514.3899</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>26167.659</t>
+          <t>18105366991.5733</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>26709.975</t>
+          <t>20925199445.1755</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>26868.102</t>
+          <t>21949377107.6185</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>27201.949</t>
+          <t>21486034538.7505</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>27611.262</t>
+          <t>23391306044.7961</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>28349.86</t>
+          <t>26281319814.0677</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>28533.803</t>
+          <t>28455021337.4572</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>28986.532</t>
+          <t>30277004574.2283</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>29625.12</t>
+          <t>29397231672.684</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>30221.823</t>
+          <t>29734087106.1845</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>28824.294</t>
+          <t>25141818278.126</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21474.27</t>
+          <t>28920.2358979004</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21728.47</t>
+          <t>35342.5066461028</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>21998.085</t>
+          <t>25850.7911245046</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>22407.136</t>
+          <t>25580.9500550331</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>23096.434</t>
+          <t>37820.8539477569</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>23762.495</t>
+          <t>56407.3862216889</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>24065.074</t>
+          <t>54136.0138994528</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>24452.873</t>
+          <t>45068.2847084017</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>24822.944</t>
+          <t>47055.8868450886</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>25528.033</t>
+          <t>59078.1995984548</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>25761.811</t>
+          <t>60729.6065917159</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>26246.008</t>
+          <t>52737.0641773251</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>26776.738</t>
+          <t>49766.1581910343</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>27188.563</t>
+          <t>45923.4768792928</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>26224.348</t>
+          <t>-3885.98186382232</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22926.401</t>
+          <t>-8415201362.77572</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>23393.047</t>
+          <t>-8148351611.14785</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>23193.963</t>
+          <t>-7826744932.35565</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>23395.733</t>
+          <t>-8896464912.31812</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>24727.143</t>
+          <t>-10051408764.6305</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>27231.804</t>
+          <t>-11939968651.3993</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>27462.149</t>
+          <t>-12977850034.4888</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>26627.768</t>
+          <t>-13237531310.951</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>27601.692</t>
+          <t>-15309804399.2166</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>30046.442</t>
+          <t>-17091450374.5429</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>30766.287</t>
+          <t>-19308612151.2101</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>31533.798</t>
+          <t>-20957038205.6647</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>30501.54</t>
+          <t>-20629218879.2154</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>31212.594</t>
+          <t>-21060941197.3445</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>28475.721</t>
+          <t>-18535739602.3972</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>261876.75135</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>271763.24793</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>277291.81396</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>263817.90514</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>287026.28536</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>324675.87616</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>314180.34</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>314996.00135</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>373546.64455</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>431441.21529</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>497102.37432</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>554050.08225</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>604152.65594</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>642542.9809</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>569907.74515</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>11046.668</t>
+          <t>0.124861798857082</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>11180.27</t>
+          <t>0.124210114718182</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11366.321</t>
+          <t>0.123086501659419</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>11416.943</t>
+          <t>0.117867167197558</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11577.091</t>
+          <t>0.121426462588617</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>11783.121</t>
+          <t>0.127551425545312</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11634.89</t>
+          <t>0.122051467848705</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11695.729</t>
+          <t>0.118231779671834</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>11792.766</t>
+          <t>0.118550007454958</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>12108.107</t>
+          <t>0.11834490174675</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>12163.9</t>
+          <t>0.120386203022068</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>12287.489</t>
+          <t>0.117161747211418</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>12470.271</t>
+          <t>0.114546241107084</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>12503.118</t>
+          <t>0.112856183231957</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>12197.981</t>
+          <t>0.102654594317442</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>305138.4016117</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>314440.841405294</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>327587.594007179</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>321065.947049094</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>338738.67643198</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>367677.601538057</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>368676.021467726</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>378844.950791367</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>445424.810033035</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>506864.549157474</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>575007.827669293</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>655840.40661744</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>729298.239529298</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>780052.462522621</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>691872.689819192</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10291.018</t>
+          <t>321482.530872517</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9985.127</t>
+          <t>332555.747059074</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>9472.979</t>
+          <t>344917.178394306</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>10360.622</t>
+          <t>338568.917487131</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>11177.327</t>
+          <t>356999.020180108</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>12553.972</t>
+          <t>386874.946130793</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>13548.641</t>
+          <t>386772.922543959</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>13796.839</t>
+          <t>396942.807451827</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>14990.942</t>
+          <t>466382.371783055</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>15948.54</t>
+          <t>530121.617754663</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>17355.517</t>
+          <t>600740.325966168</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>18323.399</t>
+          <t>683381.60813677</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>17891.356</t>
+          <t>760024.789437084</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>17948.347</t>
+          <t>810776.88984777</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>15868.391</t>
+          <t>719123.923659109</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>108.67</t>
+          <t>1806419.95744152</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>117.61</t>
+          <t>1903619.63119832</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>132.22</t>
+          <t>1991378.04293049</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>116.27</t>
+          <t>1974309.49369325</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>106.64</t>
+          <t>2102640.56365441</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>2247626.8056084</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>77.62</t>
+          <t>2293100.26203844</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.24</t>
+          <t>2404134.85737192</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>65.59</t>
+          <t>2881662.72184117</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>60.07</t>
+          <t>3334460.74685826</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>3792269.76059826</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>43.24</t>
+          <t>4335280.5429461</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>49.66</t>
+          <t>4912526.2304056</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>51.48</t>
+          <t>5281158.21733246</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>5149659.56775567</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>321482.530872517</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.941</t>
+          <t>325947.319473765</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.907</t>
+          <t>337774.685696424</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>354495.063303018</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>370432.395051855</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>389518.440916313</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.982</t>
+          <t>399415.982245792</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>407788.363459725</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>416467.695270609</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>429290.936956204</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>443943.509142482</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>459601.081846804</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>475828.49606592</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>488962.806655198</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.598</t>
+          <t>499029.311942886</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>305138.4016117</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>308275.056795181</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>321007.019242775</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>336496.742908036</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>351598.89165083</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>370233.953189679</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>381068.09338081</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>389693.276346741</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>398201.367691238</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>410914.101583178</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>425256.813912926</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>441754.755068389</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>457487.151721281</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>471507.090284196</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>481214.226599935</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>225552.845377483</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>236448.812770926</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>245111.756785694</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>232706.267192869</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>255316.205739892</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>286688.003149207</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>279876.252906041</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>284245.142758173</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>341621.137156945</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>394616.429465337</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>456536.957313832</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>507929.04306323</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>562711.414032916</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>596011.35945223</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>528636.213800891</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>21474270065.9936</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>21728470234.0654</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>21998084998.91</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>22407135998.91</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>23096433998.91</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>23762494998.91</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>24065073998.91</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>24452872998.91</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>24822943998.91</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>25528032998.91</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>25761810998.91</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>26246007998.91</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>26776737998.91</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>27188562998.91</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>26224347998.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>24163261022.4366</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>24606801459.0087</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>24972060998.11</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>25524080998.21</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>26167658998.02</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>26709974998.01</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>26868101998.04</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>27201948998.03</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>27611261998.03</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>28349859998.03</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>28533802998.04</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>28986531998.04</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>29625119998.04</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>30221823441.5849</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>28824294040.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>11046667953.8974</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>11180270435.5511</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>11366320537.7864</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>11416943343.5617</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>11577090588.8751</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>11783121082.8557</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>11634889935.7461</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>11695729319.0936</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>11792766114.5529</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>12108106728.9406</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>12163899664.5301</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>12287488573.6924</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>12470270723.1141</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>12503118170.9134</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>12197981135.2108</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>13593006.8730362</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>13739222.1632323</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>14027669.99811</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>14345414.99821</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>14719774.99802</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>15048149.99801</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>15199154.99804</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>15568199.99803</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>15901974.99803</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>16165969.99803</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>16405414.99804</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>16676749.99804</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>17046849.99804</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>17485670.859599</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>16875446.8452208</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>12163122.9926407</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>12208770.2160367</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>12428724.99891</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>12680214.99891</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>13075604.99891</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>13480109.99891</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>13707879.99891</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14047644.99891</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>14354944.99891</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>14633084.99891</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>14846974.99891</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>15135234.99891</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>15443969.99891</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>15744979.99891</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>15432784.99891</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>24163261022.4366</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>24606801459.0087</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>24972060998.11</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>25524080998.21</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>26167658998.02</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>26709974998.01</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>26868101998.04</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>27201948998.03</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>27611261998.03</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>28349859998.03</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>28533802998.04</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>28986531998.04</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>29625119998.04</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>30221823441.5849</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>28824294040.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>21474270065.9936</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>21728470234.0654</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>21998084998.91</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>22407135998.91</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>23096433998.91</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>23762494998.91</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>24065073998.91</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>24452872998.91</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>24822943998.91</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>25528032998.91</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>25761810998.91</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>26246007998.91</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>26776737998.91</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>27188562998.91</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>26224347998.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.165026836006221</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.174070473563283</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.18533569691959</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.191701460000232</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.19153353552202</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.196860559389073</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.205381127739414</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.208997566663107</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.211037923925837</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.216881218718759</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.222901783891316</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.233777121466238</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.240482936633715</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.235402302929652</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.248822892765799</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.777580178303824</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.773047863670747</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.764365399958455</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.76011374745345</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.765582903940644</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.763194950347046</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.756955280826279</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.753490805886111</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.753646248571463</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.749574489514505</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.745810508452688</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.735992500871819</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.732808213124645</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.738094910441187</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.725483562503862</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0573929821675975</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0528816592979775</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0502988998164565</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0481847893652541</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0428835575080581</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0399444874783705</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0376635887154743</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0375116248191324</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0353158250441179</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0335442894785202</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.03128770542763</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0302303754872812</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0267088480864822</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0265027844380628</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0256935423471342</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.144678943718754</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.145974864030428</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.149052670820783</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.153333749670552</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.152771261677904</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.15853507878715</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.16454051150029</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.16732354439901</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.170852123624246</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.173805592370665</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.181409266638102</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.189414445328348</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.197587086459988</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.195460971524824</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.205496764228743</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.787343230683292</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.789704952553665</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.790785016748082</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.78853463095468</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.795486394695564</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.792478849347931</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.789518127429825</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.786493111883581</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.784531397519799</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.783655875464756</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.778795042980499</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.771378760869917</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.76736959997502</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.770214247141349</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.760021404366665</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0679777902241639</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0643201481103712</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0601622780062691</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0581315854973308</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.051742310168121</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0489860399672107</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0459413277129061</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0461833104495654</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0446164479085444</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0425385029137838</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0397956607547163</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0392067640821937</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.035043283485602</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0343247502136119</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.034481796579485</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1026040.00237</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1080145.52527</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1130851.85394</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1099419.52822</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1188394.5984</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1332236.76032</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1314026.785</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1335753.48033</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1569015.20584</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1798475.86541</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2047279.31899</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2296688.91947</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2536378.0898</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2697549.842</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2392609.67465</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>547035.37625</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>569004.55983</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>590028.93518</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>571275.18468</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>612315.22592</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>673562.94928</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>666649.17545</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>681187.95021</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>808003.50894</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>924738.04722</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1057277.28328</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1191310.6512</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1322736.20347</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1406788.2493</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1247760.13746</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2478486.31468713</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2535886.67313897</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2611947.9277956</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2687320.32675744</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2769268.91957621</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2852903.90086274</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2935766.10277972</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>3017657.92971134</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3109805.33179146</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>3216840.57326967</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>3342467.02234172</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3482845.33662717</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>3624386.83491654</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3761457.24938902</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>3844141.95872883</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
